--- a/Assets/Excel/战斗实体配置表.xlsx
+++ b/Assets/Excel/战斗实体配置表.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\TurnDemo\Assets\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
@@ -138,7 +143,7 @@
     <t>攻防兼备，均衡型</t>
   </si>
   <si>
-    <t>AnimatorComponent,BattleAnimationComponent,PlayerSkillComponent,PlayerPropertyComponent,StatusComponent</t>
+    <t>AnimatorComponent,BattleAnimationComponent,PlayerSkillComponent,RoleStatComponent,StatusComponent</t>
   </si>
   <si>
     <t>10,11,12</t>
@@ -273,7 +278,7 @@
     <t>黏糊糊...</t>
   </si>
   <si>
-    <t>AnimatorComponent,BattleAnimationComponent,MonsterSkillComponent,MonsterPropertyComponent,ToughnessComponent,StatusComponent,AnimatorComponent</t>
+    <t>AnimatorComponent,BattleAnimationComponent,MonsterSkillComponent,MonsterStatComponent,ToughnessComponent,StatusComponent,AnimatorComponent</t>
   </si>
   <si>
     <t>1,2,3,4</t>
@@ -327,7 +332,7 @@
     <t>邪恶的力量</t>
   </si>
   <si>
-    <t>AnimatorComponent,BattleAnimationComponent,MonsterSkillComponent,MonsterPropertyComponent,ToughnessComponent,StatusComponent</t>
+    <t>AnimatorComponent,BattleAnimationComponent,MonsterSkillComponent,MonsterStatComponent,ToughnessComponent,StatusComponent</t>
   </si>
   <si>
     <t>103,104,105,106</t>
